--- a/data/satisfaction_detail/2026/1-8月/酒店会议主承办.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/酒店会议主承办.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.69</v>
+        <v>9.763125</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.68</v>
+        <v>9.731875</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.75</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.76</v>
+        <v>9.782500000000002</v>
       </c>
     </row>
     <row r="4">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.83</v>
+        <v>9.8828125</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.83</v>
+        <v>9.8828125</v>
       </c>
     </row>
     <row r="8">
@@ -553,7 +553,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.8453125</v>
       </c>
     </row>
     <row r="9">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.8453125</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>10</v>
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.33</v>
+        <v>9.0625</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.33</v>
+        <v>9.0625</v>
       </c>
     </row>
     <row r="13">
@@ -631,7 +631,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.8453125</v>
       </c>
     </row>
     <row r="15">
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.5</v>
+        <v>9.53125</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.5</v>
+        <v>9.53125</v>
       </c>
     </row>
     <row r="16">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.6</v>
+        <v>9.6859375</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.4</v>
+        <v>9.53125</v>
       </c>
     </row>
     <row r="18">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
     </row>
     <row r="19">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
     </row>
     <row r="20">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>9.65</v>
+        <v>9.733749999999999</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9.58</v>
+        <v>9.669062500000001</v>
       </c>
     </row>
     <row r="21">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9.83</v>
+        <v>9.8828125</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.5</v>
+        <v>9.6484375</v>
       </c>
     </row>
     <row r="22">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
     </row>
     <row r="23">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
     </row>
     <row r="24">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.8453125</v>
       </c>
     </row>
     <row r="25">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>9.33</v>
+        <v>9.382812500000002</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>9.17</v>
+        <v>9.1171875</v>
       </c>
     </row>
     <row r="26">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
     </row>
     <row r="27">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>9.5</v>
+        <v>9.6484375</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>9.67</v>
+        <v>9.765625</v>
       </c>
     </row>
     <row r="29">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9.359999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.52375</v>
       </c>
     </row>
     <row r="30">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>8.33</v>
+        <v>8.828125</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8.83</v>
+        <v>9.03125</v>
       </c>
     </row>
     <row r="31">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>9.5</v>
+        <v>9.6859375</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>9.5</v>
+        <v>9.6859375</v>
       </c>
     </row>
     <row r="32">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.8453125</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>9.6</v>
+        <v>9.6859375</v>
       </c>
     </row>
     <row r="33">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.8453125</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.6</v>
+        <v>9.6859375</v>
       </c>
     </row>
     <row r="34">
